--- a/customer_profiles/pf/templates/ym/pi.xlsx
+++ b/customer_profiles/pf/templates/ym/pi.xlsx
@@ -2,10 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28260" windowHeight="14100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="SHEET1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SHEET1'!$A$1:$H$19</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -20,262 +26,323 @@
     <numFmt numFmtId="169" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="170" formatCode="dd/mmm/yy"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="47">
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Berlin Sans FB Demi"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <color indexed="8"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="62"/>
       <sz val="15"/>
     </font>
     <font>
-      <name val="宋体"/>
+      <name val="新細明體"/>
+      <charset val="136"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
+      <charset val="136"/>
       <color indexed="9"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <color indexed="19"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <color indexed="10"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="62"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="62"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="62"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="宋体"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
+      <charset val="134"/>
       <color indexed="8"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="8"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <color indexed="20"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="10"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="9"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <b val="1"/>
       <color indexed="63"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <color indexed="62"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="新細明體"/>
+      <charset val="136"/>
       <i val="1"/>
       <color indexed="23"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="宋体"/>
-      <color theme="1"/>
-      <sz val="9"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="50">
@@ -288,258 +355,570 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="29"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="26"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="47"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="27"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="45"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="53"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="56"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="54"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="49"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="46"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="55"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
-    <border/>
+  <borders count="26">
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="56"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="27"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="27"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="56"/>
+      </top>
+      <bottom style="double">
+        <color indexed="56"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -555,208 +934,25 @@
         <color auto="1"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="medium">
-        <color theme="4" tint="0.49998"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="22"/>
-      </left>
-      <right style="thin">
-        <color indexed="22"/>
-      </right>
-      <top style="thin">
-        <color indexed="22"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="22"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thick">
-        <color indexed="56"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thick">
-        <color indexed="27"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="medium">
-        <color indexed="27"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color indexed="56"/>
-      </top>
-      <bottom style="double">
-        <color indexed="56"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="63"/>
-      </left>
-      <right style="double">
-        <color indexed="63"/>
-      </right>
-      <top style="double">
-        <color indexed="63"/>
-      </top>
-      <bottom style="double">
-        <color indexed="63"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="double">
-        <color indexed="10"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="63"/>
-      </left>
-      <right style="thin">
-        <color indexed="63"/>
-      </right>
-      <top style="thin">
-        <color indexed="63"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="63"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="117">
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="37" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
@@ -765,7 +961,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
@@ -819,10 +1015,10 @@
     <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyAlignment="1">
@@ -831,10 +1027,10 @@
     <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyAlignment="1">
@@ -843,10 +1039,10 @@
     <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyAlignment="1">
@@ -855,10 +1051,10 @@
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyAlignment="1">
@@ -867,10 +1063,10 @@
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyAlignment="1">
@@ -879,10 +1075,10 @@
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyAlignment="1">
@@ -907,157 +1103,157 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="14" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="45" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="46" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="18" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="47" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="48" borderId="19" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="49" borderId="20" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="14" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="48" borderId="22" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="19" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="46" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="18" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="47" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="48" borderId="19" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="49" borderId="20" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="48" borderId="22" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="39" borderId="19" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1091,44 +1287,53 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="left" vertical="center"/>
@@ -1139,8 +1344,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1154,8 +1360,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
@@ -1172,8 +1379,9 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1181,20 +1389,24 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
@@ -1247,8 +1459,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
@@ -1277,11 +1490,13 @@
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
-      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1289,20 +1504,24 @@
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="left" vertical="center"/>
@@ -1313,8 +1532,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -1329,8 +1549,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="87">
       <alignment vertical="center"/>
@@ -1356,22 +1577,31 @@
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1379,78 +1609,80 @@
     <xf numFmtId="168" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="76">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="45" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="45" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="99">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="75">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="55">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="55">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="117">
-    <cellStyle name="常规" xfId="0"/>
-    <cellStyle name="千位分隔" xfId="1"/>
-    <cellStyle name="货币" xfId="2"/>
-    <cellStyle name="百分比" xfId="3"/>
-    <cellStyle name="千位分隔[0]" xfId="4"/>
-    <cellStyle name="货币[0]" xfId="5"/>
-    <cellStyle name="超链接" xfId="6"/>
-    <cellStyle name="已访问的超链接" xfId="7"/>
-    <cellStyle name="注释" xfId="8"/>
-    <cellStyle name="警告文本" xfId="9"/>
-    <cellStyle name="标题" xfId="10"/>
-    <cellStyle name="解释性文本" xfId="11"/>
-    <cellStyle name="标题 1" xfId="12"/>
-    <cellStyle name="标题 2" xfId="13"/>
-    <cellStyle name="标题 3" xfId="14"/>
-    <cellStyle name="标题 4" xfId="15"/>
-    <cellStyle name="输入" xfId="16"/>
-    <cellStyle name="输出" xfId="17"/>
-    <cellStyle name="计算" xfId="18"/>
-    <cellStyle name="检查单元格" xfId="19"/>
-    <cellStyle name="链接单元格" xfId="20"/>
-    <cellStyle name="汇总" xfId="21"/>
-    <cellStyle name="好" xfId="22"/>
-    <cellStyle name="差" xfId="23"/>
-    <cellStyle name="适中" xfId="24"/>
-    <cellStyle name="强调文字颜色 1" xfId="25"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
-    <cellStyle name="强调文字颜色 2" xfId="29"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
-    <cellStyle name="强调文字颜色 3" xfId="33"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
-    <cellStyle name="强调文字颜色 4" xfId="37"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
-    <cellStyle name="强调文字颜色 5" xfId="41"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
-    <cellStyle name="强调文字颜色 6" xfId="45"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="20% - 輔色1" xfId="49"/>
     <cellStyle name="20% - 輔色2" xfId="50"/>
     <cellStyle name="20% - 輔色3" xfId="51"/>
@@ -1520,6 +1752,7 @@
     <cellStyle name="样式 1 2" xfId="115"/>
     <cellStyle name="中等" xfId="116"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1608,7 +1841,7 @@
     </to>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="/xl/media/image1.png"/>
+        <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </cNvPicPr>
@@ -1620,8 +1853,16 @@
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
-        <a:ln>
+        <a:xfrm>
+          <a:off x="5080" y="5080"/>
+          <a:ext cx="1511935" cy="655320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1674,14 +1915,74 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1737,7 +2038,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -1746,13 +2047,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1786,6 +2087,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1840,6 +2152,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
@@ -1847,10 +2160,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="11.60000038146973"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
     <col width="17.625" customWidth="1" style="3" min="1" max="1"/>
     <col width="13.375" customWidth="1" style="3" min="2" max="2"/>
@@ -1922,7 +2235,7 @@
       <c r="J4" s="69" t="n"/>
       <c r="K4" s="69" t="n"/>
     </row>
-    <row r="5" ht="15.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="5" ht="15.95" customFormat="1" customHeight="1" s="65">
       <c r="A5" s="73" t="n"/>
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="71" t="n"/>
@@ -1935,7 +2248,7 @@
       <c r="J5" s="69" t="n"/>
       <c r="K5" s="69" t="n"/>
     </row>
-    <row r="6" ht="12.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="6" ht="12.95" customFormat="1" customHeight="1" s="65">
       <c r="A6" s="73" t="inlineStr">
         <is>
           <t>PI Number:</t>
@@ -1956,7 +2269,7 @@
       <c r="J6" s="69" t="n"/>
       <c r="K6" s="69" t="n"/>
     </row>
-    <row r="7" ht="12.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="7" ht="12.95" customFormat="1" customHeight="1" s="65">
       <c r="A7" s="73" t="inlineStr">
         <is>
           <t>Incoterm:</t>
@@ -1981,7 +2294,7 @@
       <c r="J7" s="69" t="n"/>
       <c r="K7" s="69" t="n"/>
     </row>
-    <row r="8" ht="12.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="8" ht="12.95" customFormat="1" customHeight="1" s="65">
       <c r="A8" s="73" t="inlineStr">
         <is>
           <t>Payment Terms:</t>
@@ -2006,7 +2319,7 @@
       <c r="J8" s="69" t="n"/>
       <c r="K8" s="69" t="n"/>
     </row>
-    <row r="9" ht="12.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="9" ht="12.95" customFormat="1" customHeight="1" s="65">
       <c r="A9" s="80" t="n"/>
       <c r="B9" s="71" t="n"/>
       <c r="C9" s="71" t="n"/>
@@ -2019,7 +2332,7 @@
       <c r="J9" s="69" t="n"/>
       <c r="K9" s="69" t="n"/>
     </row>
-    <row r="10" ht="12.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="10" ht="12.95" customFormat="1" customHeight="1" s="65">
       <c r="A10" s="80" t="inlineStr">
         <is>
           <t>Bill To:</t>
@@ -2048,7 +2361,7 @@
       <c r="J10" s="69" t="n"/>
       <c r="K10" s="69" t="n"/>
     </row>
-    <row r="11" ht="12.94999980926514" customFormat="1" customHeight="1" s="65">
+    <row r="11" ht="12.95" customFormat="1" customHeight="1" s="65">
       <c r="A11" s="89" t="n"/>
       <c r="B11" s="90" t="n"/>
       <c r="C11" s="91" t="n"/>
@@ -2061,7 +2374,7 @@
       <c r="J11" s="69" t="n"/>
       <c r="K11" s="69" t="n"/>
     </row>
-    <row r="12" ht="12.94999980926514" customFormat="1" customHeight="1" s="92">
+    <row r="12" ht="12.95" customFormat="1" customHeight="1" s="92">
       <c r="A12" s="80" t="n"/>
       <c r="B12" s="90" t="n"/>
       <c r="C12" s="91" t="n"/>
@@ -2074,7 +2387,7 @@
       <c r="J12" s="94" t="n"/>
       <c r="K12" s="94" t="n"/>
     </row>
-    <row r="13" ht="12.94999980926514" customFormat="1" customHeight="1" s="92">
+    <row r="13" ht="12.95" customFormat="1" customHeight="1" s="92">
       <c r="A13" s="80" t="n"/>
       <c r="B13" s="86" t="n"/>
       <c r="C13" s="86" t="n"/>
@@ -2087,7 +2400,7 @@
       <c r="J13" s="94" t="n"/>
       <c r="K13" s="94" t="n"/>
     </row>
-    <row r="14" ht="12.94999980926514" customFormat="1" customHeight="1" s="92">
+    <row r="14" ht="12.95" customFormat="1" customHeight="1" s="92">
       <c r="A14" s="73" t="inlineStr">
         <is>
           <t>Port of Loading:</t>
@@ -2114,7 +2427,7 @@
       <c r="J14" s="94" t="n"/>
       <c r="K14" s="94" t="n"/>
     </row>
-    <row r="15" ht="17.10000038146973" customFormat="1" customHeight="1" s="92">
+    <row r="15" ht="17.1" customFormat="1" customHeight="1" s="92">
       <c r="A15" s="73" t="inlineStr">
         <is>
           <t>Final Destination</t>
@@ -2138,18 +2451,18 @@
           <t>WEIHAI E-MAX SPORT APPARATUS CO.LTD</t>
         </is>
       </c>
-      <c r="H15" s="88" t="n"/>
+      <c r="H15" s="101" t="n"/>
       <c r="I15" s="96" t="n"/>
       <c r="J15" s="94" t="n"/>
       <c r="K15" s="94" t="n"/>
     </row>
-    <row r="16" ht="15.94999980926514" customFormat="1" customHeight="1" s="92">
+    <row r="16" ht="15.95" customFormat="1" customHeight="1" s="92">
       <c r="A16" s="73" t="inlineStr">
         <is>
           <t>Number of Cartons</t>
         </is>
       </c>
-      <c r="B16" s="101" t="n"/>
+      <c r="B16" s="102" t="n"/>
       <c r="C16" s="86" t="n"/>
       <c r="D16" s="86" t="n"/>
       <c r="E16" s="86" t="n"/>
@@ -2158,12 +2471,12 @@
           <t>Actual Manufacturer Company Address</t>
         </is>
       </c>
-      <c r="G16" s="102" t="inlineStr">
-        <is>
-          <t>NO. 93 GRAPE BEACH ROAD</t>
-        </is>
-      </c>
-      <c r="H16" s="103" t="n"/>
+      <c r="G16" s="103" t="inlineStr">
+        <is>
+          <t>NO.25 TONGYI NORTH ROAD,</t>
+        </is>
+      </c>
+      <c r="H16" s="104" t="n"/>
       <c r="I16" s="96" t="n"/>
       <c r="J16" s="94" t="n"/>
       <c r="K16" s="94" t="n"/>
@@ -2175,17 +2488,17 @@
       <c r="D17" s="86" t="n"/>
       <c r="E17" s="86" t="n"/>
       <c r="F17" s="93" t="n"/>
-      <c r="G17" s="104" t="inlineStr">
-        <is>
-          <t>SUNJIATUAN TOWN, WEIHAI，SHANGDONG, CHINA</t>
-        </is>
-      </c>
-      <c r="H17" s="105" t="n"/>
+      <c r="G17" s="105" t="inlineStr">
+        <is>
+          <t>HUANCUI DISTRICT, WEIHAI, SHANDONG, CHINA.</t>
+        </is>
+      </c>
+      <c r="H17" s="106" t="n"/>
       <c r="I17" s="96" t="n"/>
       <c r="J17" s="94" t="n"/>
       <c r="K17" s="94" t="n"/>
     </row>
-    <row r="18" ht="15.94999980926514" customHeight="1" s="106">
+    <row r="18" ht="15.95" customHeight="1" s="107">
       <c r="A18" s="46" t="n"/>
       <c r="B18" s="47" t="n"/>
       <c r="C18" s="47" t="n"/>
@@ -2196,7 +2509,7 @@
       <c r="H18" s="47" t="n"/>
       <c r="I18" s="46" t="n"/>
     </row>
-    <row r="19" ht="24" customHeight="1" s="106">
+    <row r="19" ht="24" customHeight="1" s="107">
       <c r="A19" s="48" t="inlineStr">
         <is>
           <t>Country of The Origin</t>
@@ -2222,7 +2535,7 @@
           <t xml:space="preserve">Description </t>
         </is>
       </c>
-      <c r="F19" s="107" t="inlineStr">
+      <c r="F19" s="108" t="inlineStr">
         <is>
           <t>USD Unit Price</t>
         </is>
@@ -2232,7 +2545,7 @@
           <t>Quantity</t>
         </is>
       </c>
-      <c r="H19" s="108" t="inlineStr">
+      <c r="H19" s="109" t="inlineStr">
         <is>
           <t xml:space="preserve">USD Amount </t>
         </is>
@@ -2243,24 +2556,26 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="17.39999961853027" customHeight="1" s="106">
-      <c r="A20" s="109" t="n"/>
-      <c r="B20" s="109" t="n"/>
-      <c r="C20" s="109" t="n"/>
-      <c r="D20" s="109" t="n"/>
-      <c r="E20" s="110" t="n"/>
-      <c r="F20" s="111" t="n"/>
-      <c r="G20" s="109" t="n"/>
-      <c r="H20" s="111" t="n"/>
-      <c r="I20" s="112" t="n"/>
+    <row r="20" ht="17.39999961853027" customHeight="1" s="107">
+      <c r="A20" s="110" t="n"/>
+      <c r="B20" s="110" t="n"/>
+      <c r="C20" s="110" t="n"/>
+      <c r="D20" s="110" t="n"/>
+      <c r="E20" s="111" t="n"/>
+      <c r="F20" s="112" t="n"/>
+      <c r="G20" s="110" t="n"/>
+      <c r="H20" s="112" t="n"/>
+      <c r="I20" s="113" t="n"/>
+      <c r="J20" s="114" t="n"/>
+      <c r="K20" s="114" t="n"/>
     </row>
-    <row r="21" ht="12.35000038146973" customHeight="1" s="106">
+    <row r="21" ht="14.35" customHeight="1" s="107">
       <c r="A21" s="47" t="n"/>
       <c r="B21" s="47" t="n"/>
       <c r="C21" s="47" t="n"/>
       <c r="D21" s="47" t="n"/>
       <c r="E21" s="46" t="n"/>
-      <c r="F21" s="113" t="inlineStr">
+      <c r="F21" s="115" t="inlineStr">
         <is>
           <t xml:space="preserve">Sub-Total </t>
         </is>
@@ -2269,14 +2584,14 @@
       <c r="H21" s="56" t="n"/>
       <c r="I21" s="46" t="n"/>
     </row>
-    <row r="22" ht="12.35000038146973" customHeight="1" s="106">
+    <row r="22" ht="14.35" customHeight="1" s="107">
       <c r="A22" s="47" t="n"/>
       <c r="B22" s="47" t="n"/>
       <c r="C22" s="47" t="n"/>
       <c r="D22" s="47" t="n"/>
       <c r="E22" s="47" t="n"/>
       <c r="F22" s="46" t="n"/>
-      <c r="G22" s="114" t="inlineStr">
+      <c r="G22" s="116" t="inlineStr">
         <is>
           <t>TOTAL EXCLUDING EXCISE TAX  (USD)</t>
         </is>
@@ -2284,7 +2599,7 @@
       <c r="H22" s="58" t="n"/>
       <c r="I22" s="46" t="n"/>
     </row>
-    <row r="23" ht="12.35000038146973" customHeight="1" s="106">
+    <row r="23" ht="14.35" customHeight="1" s="107">
       <c r="A23" s="46" t="n"/>
       <c r="B23" s="46" t="n"/>
       <c r="C23" s="46" t="n"/>
@@ -2325,7 +2640,7 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="G25" s="115" t="n"/>
+      <c r="G25" s="117" t="n"/>
       <c r="H25" s="64" t="n"/>
       <c r="I25" s="46" t="n"/>
     </row>
@@ -2358,7 +2673,8 @@
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G17:H17"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.196850393700787" right="0.236220472440945" top="0.47244094488189" bottom="0.511811023622047" header="0.236220472440945" footer="0.196850393700787"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="73" verticalDpi="203"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>